--- a/老虎机数学专题-Megaways数学.xlsx
+++ b/老虎机数学专题-Megaways数学.xlsx
@@ -3987,6 +3987,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:T95" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6014,5 +6017,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M96" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机数学专题-Megaways数学.xlsx
+++ b/老虎机数学专题-Megaways数学.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="Megaways 滚轮→Way计算→RTP" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1108,7 +1108,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1162,6 +1162,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2191,1777 +2215,1777 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:10">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="18" t="s">
+      <c r="B18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="18" t="s">
+      <c r="A19" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1" spans="1:10">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="18" t="s">
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="18" t="s">
+      <c r="B21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="18" t="s">
+      <c r="B22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="18" t="s">
+      <c r="B23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="18" t="s">
+      <c r="A24" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="33" customHeight="1" spans="1:10">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="18" t="s">
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="18" t="s">
+      <c r="B26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="18" t="s">
+      <c r="B27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="18" t="s">
+      <c r="A28" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="18" t="s">
+      <c r="B29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="18" t="s">
+      <c r="B30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="18" t="s">
+      <c r="B31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="18" t="s">
+      <c r="A32" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1" spans="1:10">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="18" t="s">
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="18" t="s">
+      <c r="B34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="18" t="s">
+      <c r="B35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="18" t="s">
+      <c r="B36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="18" t="s">
+      <c r="B37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="18" t="s">
+      <c r="B38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="18" t="s">
+      <c r="B39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="18" t="s">
+      <c r="B40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="18" t="s">
+      <c r="B41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="18" t="s">
+      <c r="B42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="18" t="s">
+      <c r="B43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="18" t="s">
+      <c r="A44" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="18" t="s">
+      <c r="B45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="18" t="s">
+      <c r="B46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="18" t="s">
+      <c r="B47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="18" t="s">
+      <c r="A48" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="33" customHeight="1" spans="1:15">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="18" t="s">
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="18" t="s">
+      <c r="B50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="18" t="s">
+      <c r="B51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="18" t="s">
+      <c r="B52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="18" t="s">
+      <c r="B53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:15">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C54" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="18" t="s">
+      <c r="C54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="36" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B56" s="26" t="s">
+      <c r="B56" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
-      <c r="M56" s="26"/>
-      <c r="N56" s="26"/>
-      <c r="O56" s="26"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="36"/>
+      <c r="O56" s="36"/>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="18" t="s">
+      <c r="A57" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="20.25" customHeight="1" spans="1:15">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="18" t="s">
+      <c r="B58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="18" t="s">
+      <c r="A59" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="18" t="s">
+      <c r="B60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="18" t="s">
+      <c r="B61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="33" customHeight="1" spans="1:15">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="18" t="s">
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="18" t="s">
+      <c r="B63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A64" s="22" t="s">
+      <c r="A64" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64" s="18" t="s">
+      <c r="B64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="33" customHeight="1" spans="1:10">
-      <c r="A65" s="22" t="s">
+      <c r="A65" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="18" t="s">
+      <c r="B65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="33" customHeight="1" spans="1:10">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="18" t="s">
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="33" customHeight="1" spans="1:10">
-      <c r="A67" s="22" t="s">
+      <c r="A67" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="18" t="s">
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="B68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="18" t="s">
+      <c r="B68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I69" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69" s="18" t="s">
+      <c r="A69" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:10">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I70" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J70" s="18" t="s">
+      <c r="C70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J70" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A71" s="25" t="s">
+      <c r="A71" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B71" s="26" t="s">
+      <c r="B71" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I71" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71" s="18" t="s">
+      <c r="C71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A72" s="25" t="s">
+      <c r="A72" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="26" t="s">
+      <c r="B72" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I72" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="18" t="s">
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I72" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="B73" s="26" t="s">
+      <c r="B73" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="C73" s="26"/>
-      <c r="D73" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I73" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="18" t="s">
+      <c r="C73" s="36"/>
+      <c r="D73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="26" t="s">
+      <c r="B74" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="C74" s="26"/>
-      <c r="D74" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I74" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J74" s="18" t="s">
+      <c r="C74" s="36"/>
+      <c r="D74" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I74" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A75" s="25" t="s">
+      <c r="A75" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B75" s="26" t="s">
+      <c r="B75" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="C75" s="26"/>
-      <c r="D75" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="I75" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75" s="18" t="s">
+      <c r="C75" s="36"/>
+      <c r="D75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="28" t="s">
         <v>1</v>
       </c>
     </row>
